--- a/Consolidated_QCF_Result.xlsx
+++ b/Consolidated_QCF_Result.xlsx
@@ -647,6 +647,56 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -671,56 +721,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -729,7 +729,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
@@ -913,17 +913,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="28" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="28" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1020,6 +1011,111 @@
     <xf numFmtId="43" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1071,110 +1167,11 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="28" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -1187,14 +1184,14 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1243,11 +1240,11 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1702,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.21875" defaultRowHeight="13.2"/>
   <cols>
     <col width="5.5546875" customWidth="1" style="2" min="1" max="1"/>
@@ -1712,7 +1709,7 @@
     <col width="6.5546875" customWidth="1" style="2" min="6" max="6"/>
     <col width="5.77734375" customWidth="1" style="2" min="7" max="7"/>
     <col width="18.5546875" customWidth="1" style="2" min="8" max="11"/>
-    <col width="18.5546875" customWidth="1" style="160" min="12" max="13"/>
+    <col width="18.5546875" customWidth="1" style="159" min="12" max="13"/>
     <col width="15.21875" customWidth="1" style="2" min="14" max="14"/>
     <col width="12.21875" customWidth="1" style="2" min="15" max="21"/>
     <col width="9.21875" customWidth="1" style="2" min="22" max="16384"/>
@@ -1720,7 +1717,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="29" t="n"/>
-      <c r="B1" s="136" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>LEADER ENERGY CAPITAL SDN BHD</t>
         </is>
@@ -1729,7 +1726,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="29" t="n"/>
-      <c r="B2" s="112" t="inlineStr">
+      <c r="B2" s="144" t="inlineStr">
         <is>
           <t>Quote comparison form  - Commercial and Technical Recommendation</t>
         </is>
@@ -1768,7 +1765,7 @@
           <t>RO:</t>
         </is>
       </c>
-      <c r="C3" s="137" t="n"/>
+      <c r="C3" s="107" t="n"/>
       <c r="F3" s="44" t="inlineStr">
         <is>
           <t> </t>
@@ -1805,7 +1802,7 @@
         </is>
       </c>
       <c r="M3" s="51" t="n"/>
-      <c r="N3" s="85" t="n"/>
+      <c r="N3" s="82" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="29" t="n"/>
@@ -1870,66 +1867,70 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="29" t="n"/>
-      <c r="B5" s="161" t="inlineStr">
+      <c r="B5" s="160" t="inlineStr">
         <is>
           <t>Descriptions</t>
         </is>
       </c>
-      <c r="C5" s="162" t="n"/>
-      <c r="D5" s="162" t="n"/>
-      <c r="E5" s="163" t="n"/>
-      <c r="F5" s="164" t="inlineStr">
+      <c r="C5" s="161" t="n"/>
+      <c r="D5" s="161" t="n"/>
+      <c r="E5" s="162" t="n"/>
+      <c r="F5" s="163" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="G5" s="164" t="inlineStr">
+      <c r="G5" s="163" t="inlineStr">
         <is>
           <t>UOM</t>
         </is>
       </c>
-      <c r="H5" s="165" t="inlineStr">
+      <c r="H5" s="164" t="inlineStr">
         <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="I5" s="162" t="n"/>
-      <c r="J5" s="162" t="n"/>
-      <c r="K5" s="162" t="n"/>
-      <c r="L5" s="162" t="n"/>
-      <c r="M5" s="166" t="n"/>
+      <c r="I5" s="161" t="n"/>
+      <c r="J5" s="161" t="n"/>
+      <c r="K5" s="161" t="n"/>
+      <c r="L5" s="161" t="n"/>
+      <c r="M5" s="165" t="n"/>
       <c r="N5" s="18" t="n"/>
     </row>
     <row r="6" ht="33" customHeight="1">
       <c r="A6" s="29" t="n"/>
-      <c r="B6" s="167" t="n"/>
-      <c r="E6" s="168" t="n"/>
-      <c r="F6" s="169" t="n"/>
-      <c r="G6" s="169" t="n"/>
-      <c r="H6" s="170" t="inlineStr">
-        <is>
-          <t>PenTech Solution Sdn Bhd (740957-T)</t>
-        </is>
-      </c>
-      <c r="I6" s="171" t="n"/>
-      <c r="J6" s="158" t="inlineStr">
-        <is>
-          <t>Technovation Consulting Sdn Bhd</t>
-        </is>
-      </c>
-      <c r="K6" s="163" t="n"/>
-      <c r="L6" s="172" t="n"/>
-      <c r="M6" s="163" t="n"/>
+      <c r="B6" s="166" t="n"/>
+      <c r="E6" s="167" t="n"/>
+      <c r="F6" s="168" t="n"/>
+      <c r="G6" s="168" t="n"/>
+      <c r="H6" s="169" t="inlineStr">
+        <is>
+          <t>UMEDIC</t>
+        </is>
+      </c>
+      <c r="I6" s="170" t="n"/>
+      <c r="J6" s="128" t="inlineStr">
+        <is>
+          <t>AZONIC</t>
+        </is>
+      </c>
+      <c r="K6" s="162" t="n"/>
+      <c r="L6" s="171" t="inlineStr">
+        <is>
+          <t>CERT ACADEMY</t>
+        </is>
+      </c>
+      <c r="M6" s="162" t="n"/>
       <c r="N6" s="18" t="n"/>
     </row>
     <row r="7" ht="15.6" customHeight="1">
       <c r="A7" s="29" t="n"/>
-      <c r="B7" s="173" t="n"/>
-      <c r="C7" s="174" t="n"/>
-      <c r="D7" s="174" t="n"/>
-      <c r="E7" s="175" t="n"/>
-      <c r="F7" s="176" t="n"/>
-      <c r="G7" s="176" t="n"/>
+      <c r="B7" s="172" t="n"/>
+      <c r="C7" s="173" t="n"/>
+      <c r="D7" s="173" t="n"/>
+      <c r="E7" s="174" t="n"/>
+      <c r="F7" s="175" t="n"/>
+      <c r="G7" s="175" t="n"/>
       <c r="H7" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve"> Rate (MYR) </t>
@@ -1950,7 +1951,7 @@
           <t xml:space="preserve"> Amount (MYR) </t>
         </is>
       </c>
-      <c r="L7" s="87" t="inlineStr">
+      <c r="L7" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"> Rate (MYR) </t>
         </is>
@@ -1963,901 +1964,1682 @@
       <c r="N7" s="18" t="n"/>
     </row>
     <row r="8" ht="19.8" customHeight="1">
-      <c r="A8" s="99" t="n"/>
-      <c r="B8" s="100" t="n">
+      <c r="A8" s="96" t="n"/>
+      <c r="B8" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="177" t="inlineStr">
-        <is>
-          <t>Dell Pro Max Tower T2 Desktop</t>
-        </is>
-      </c>
-      <c r="D8" s="178" t="n"/>
-      <c r="E8" s="179" t="n"/>
-      <c r="F8" s="101" t="n">
+      <c r="C8" s="176" t="inlineStr">
+        <is>
+          <t>Standard Accessories:
+Slim carrying case for HeartStart HS1
+Brand / Origin : Philips Healthcare / USA
+Code : M5076A
+HS1 Adult SMART Pads Cartridge
+Brand / Origin : Philips Healthcare / USA
+Code : M5071A
+Battery for HeartStart HS1 AED
+Brand / Origin : Philips Healthcare / USA
+Code : M5070A
+AED Cabinet c/w alarm and break glass key box
+Brand / Origin : Local, Malaysia
+AED Wall Sign
+Brand / Origin : Local, Malaysia
+CPR &amp; AED Poster
+Size: A3</t>
+        </is>
+      </c>
+      <c r="D8" s="177" t="n"/>
+      <c r="E8" s="178" t="n"/>
+      <c r="F8" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="102" t="inlineStr">
+      <c r="G8" s="99" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="H8" s="180" t="n">
-        <v>17900</v>
-      </c>
-      <c r="I8" s="181" t="n">
-        <v>17900</v>
-      </c>
-      <c r="J8" s="180" t="n">
-        <v>13612</v>
-      </c>
-      <c r="K8" s="182" t="n">
-        <v>13612</v>
-      </c>
-      <c r="L8" s="183" t="n"/>
-      <c r="M8" s="182" t="n"/>
+      <c r="H8" s="179" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="179" t="n"/>
+      <c r="K8" s="181" t="n"/>
+      <c r="L8" s="182" t="n"/>
+      <c r="M8" s="181" t="n"/>
       <c r="N8" s="18" t="n"/>
-      <c r="O8" s="135" t="n"/>
+      <c r="O8" s="105" t="n"/>
     </row>
     <row r="9" ht="19.8" customHeight="1">
-      <c r="A9" s="127" t="n"/>
+      <c r="A9" s="132" t="n"/>
       <c r="B9" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="184" t="n"/>
-      <c r="D9" s="174" t="n"/>
-      <c r="E9" s="175" t="n"/>
-      <c r="F9" s="96" t="n"/>
-      <c r="G9" s="97" t="n"/>
-      <c r="H9" s="185" t="n"/>
-      <c r="I9" s="186" t="n"/>
-      <c r="J9" s="185" t="n"/>
-      <c r="K9" s="187" t="n"/>
-      <c r="L9" s="188" t="n"/>
-      <c r="M9" s="187" t="n"/>
+      <c r="C9" s="183" t="inlineStr">
+        <is>
+          <t>Extracted Total (Please verify PDF for line items)</t>
+        </is>
+      </c>
+      <c r="D9" s="173" t="n"/>
+      <c r="E9" s="174" t="n"/>
+      <c r="F9" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="94" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="H9" s="184" t="n"/>
+      <c r="I9" s="185" t="n"/>
+      <c r="J9" s="184" t="n">
+        <v>6900</v>
+      </c>
+      <c r="K9" s="186" t="n">
+        <v>6900</v>
+      </c>
+      <c r="L9" s="187" t="n"/>
+      <c r="M9" s="186" t="n"/>
       <c r="N9" s="18" t="n"/>
-      <c r="O9" s="135" t="n"/>
-      <c r="P9" s="135" t="n"/>
-      <c r="Q9" s="135" t="n"/>
-      <c r="R9" s="135" t="n"/>
-      <c r="S9" s="135" t="n"/>
-      <c r="T9" s="135" t="n"/>
-      <c r="U9" s="135" t="n"/>
-      <c r="V9" s="135" t="n"/>
-      <c r="W9" s="135" t="n"/>
+      <c r="O9" s="105" t="n"/>
+      <c r="P9" s="105" t="n"/>
+      <c r="Q9" s="105" t="n"/>
+      <c r="R9" s="105" t="n"/>
+      <c r="S9" s="105" t="n"/>
+      <c r="T9" s="105" t="n"/>
+      <c r="U9" s="105" t="n"/>
+      <c r="V9" s="105" t="n"/>
+      <c r="W9" s="105" t="n"/>
     </row>
     <row r="10" ht="19.8" customHeight="1">
-      <c r="A10" s="127" t="n"/>
+      <c r="A10" s="132" t="n"/>
       <c r="B10" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="123" t="n"/>
-      <c r="D10" s="123" t="n"/>
-      <c r="E10" s="123" t="n"/>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="106" t="n"/>
-      <c r="H10" s="185" t="n"/>
-      <c r="I10" s="186" t="n"/>
-      <c r="J10" s="189" t="n"/>
-      <c r="K10" s="187" t="n"/>
-      <c r="L10" s="188" t="n"/>
-      <c r="M10" s="187" t="n"/>
+      <c r="C10" s="155" t="inlineStr">
+        <is>
+          <t>Primedic HeartSave Y8
+▪ Semi-automated
+▪ Weight: 2.5kg 22 x 9.7 x 29.6cm (LxWxH)
+Comes with:
+▪ Pre-installed with 4 Language options in the AED
+(Bahasa Malaysia, English, Mandarin, Tamil)
+▪ Advanced Technology with higher efficiency delivering shock levels up
+to 360J
+▪ Warranty for AED Device: 5+3 Years*
+*Extra 3 years limited warranty.
+▪ 2-in-1 Adult &amp; Children electrode pads and comes together with Real-
+time CPR Feedback Sensor device [Lifespan: 5 years]
+▪ Battery Lifespan: up to 5 years / 150 shocks
+▪ Dust &amp; Water Resistance: IP55
+▪ Drop Resistance: 1.6 meter
+▪ CPR Kit included
+(Safety scissors, disposable hair removing knife, mouth to mouth mask
+&amp; disposable latex glove)
+▪ Adaptive volume output for hearing instructions clearly even in noisy
+environments
+▪ Automatic daily self-test for a peace of mind and cost saving
+▪ Latest AHA-2025 guidelines compliant
+*E xtra 3 years limited warranty
+*Delivery within the Klang Valley (KV) is free of charge. Deliveries outside the KV
+area (West Malaysia and East Malaysia) will incur additional fees</t>
+        </is>
+      </c>
+      <c r="D10" s="155" t="n"/>
+      <c r="E10" s="155" t="n"/>
+      <c r="F10" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H10" s="184" t="n"/>
+      <c r="I10" s="185" t="n"/>
+      <c r="J10" s="188" t="n"/>
+      <c r="K10" s="186" t="n"/>
+      <c r="L10" s="187" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M10" s="186" t="n">
+        <v>10000</v>
+      </c>
       <c r="N10" s="18" t="n"/>
-      <c r="O10" s="135" t="n"/>
-      <c r="P10" s="135" t="n"/>
-      <c r="Q10" s="135" t="n"/>
-      <c r="R10" s="135" t="n"/>
-      <c r="S10" s="135" t="n"/>
-      <c r="T10" s="135" t="n"/>
-      <c r="U10" s="135" t="n"/>
-      <c r="V10" s="135" t="n"/>
-      <c r="W10" s="135" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="O10" s="105" t="n"/>
+      <c r="P10" s="105" t="n"/>
+      <c r="Q10" s="105" t="n"/>
+      <c r="R10" s="105" t="n"/>
+      <c r="S10" s="105" t="n"/>
+      <c r="T10" s="105" t="n"/>
+      <c r="U10" s="105" t="n"/>
+      <c r="V10" s="105" t="n"/>
+      <c r="W10" s="105" t="n"/>
+    </row>
+    <row r="11" ht="19.8" customHeight="1">
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="97" t="n"/>
+      <c r="C11" s="176" t="inlineStr">
+        <is>
+          <t>CPR &amp; AED Physical Awareness Training Included (Within Klang
+Valley ONLY)
+*3 0 pax per session.
+*Certificate of Achievement for company will be provided.
+*Travelling or outstation charges will be applicable for locations outside Klang Valley</t>
+        </is>
+      </c>
+      <c r="D11" s="177" t="n"/>
+      <c r="E11" s="178" t="n"/>
+      <c r="F11" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H11" s="179" t="n"/>
+      <c r="I11" s="180" t="n"/>
+      <c r="J11" s="179" t="n"/>
+      <c r="K11" s="181" t="n"/>
+      <c r="L11" s="182" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M11" s="181" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="105" t="n"/>
+    </row>
+    <row r="12" ht="19.8" customHeight="1">
+      <c r="A12" s="132" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="183" t="inlineStr">
+        <is>
+          <t>C PR &amp; AED Interactive Video Briefing</t>
+        </is>
+      </c>
+      <c r="D12" s="173" t="n"/>
+      <c r="E12" s="174" t="n"/>
+      <c r="F12" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H12" s="184" t="n"/>
+      <c r="I12" s="185" t="n"/>
+      <c r="J12" s="184" t="n"/>
+      <c r="K12" s="186" t="n"/>
+      <c r="L12" s="187" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M12" s="186" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="105" t="n"/>
+    </row>
+    <row r="13" ht="19.8" customHeight="1">
+      <c r="A13" s="132" t="n"/>
+      <c r="B13" s="55" t="n"/>
+      <c r="C13" s="155" t="inlineStr">
+        <is>
+          <t>FREE 10 Years Basic Occupational First Aid CPR &amp; AED Training
+Public Class (For 3 Times Renewal COMPETENCY Certification)
+*Applicable for SHO or Safety Personnel</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="n"/>
+      <c r="E13" s="173" t="n"/>
+      <c r="F13" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H13" s="184" t="n"/>
+      <c r="I13" s="185" t="n"/>
+      <c r="J13" s="188" t="n"/>
+      <c r="K13" s="186" t="n"/>
+      <c r="L13" s="187" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M13" s="186" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="105" t="n"/>
+    </row>
+    <row r="14" ht="19.8" customHeight="1">
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="97" t="n"/>
+      <c r="C14" s="176" t="inlineStr">
+        <is>
+          <t>F REE AED Pad Program
+*If your Primedic HeartSave AED is used in a workplace SCA, we’ll provide a FREE PAD
+replacement within 5 years</t>
+        </is>
+      </c>
+      <c r="D14" s="177" t="n"/>
+      <c r="E14" s="178" t="n"/>
+      <c r="F14" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H14" s="179" t="n"/>
+      <c r="I14" s="180" t="n"/>
+      <c r="J14" s="179" t="n"/>
+      <c r="K14" s="181" t="n"/>
+      <c r="L14" s="182" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="181" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="105" t="n"/>
+    </row>
+    <row r="15" ht="19.8" customHeight="1">
+      <c r="A15" s="132" t="n"/>
+      <c r="B15" s="55" t="n"/>
+      <c r="C15" s="183" t="inlineStr">
+        <is>
+          <t>CERT Heartbeat Program
+*We will give a FREE AED device to SCA survivors saved by a Primedic Yuwell AED, which
+they can donate to any organization to help save more lives</t>
+        </is>
+      </c>
+      <c r="D15" s="173" t="n"/>
+      <c r="E15" s="174" t="n"/>
+      <c r="F15" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H15" s="184" t="n"/>
+      <c r="I15" s="185" t="n"/>
+      <c r="J15" s="184" t="n"/>
+      <c r="K15" s="186" t="n"/>
+      <c r="L15" s="187" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M15" s="186" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="105" t="n"/>
+    </row>
+    <row r="16" ht="19.8" customHeight="1">
+      <c r="A16" s="132" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="155" t="inlineStr">
+        <is>
+          <t>CPR Poster
+AED Poster</t>
+        </is>
+      </c>
+      <c r="D16" s="173" t="n"/>
+      <c r="E16" s="173" t="n"/>
+      <c r="F16" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H16" s="184" t="n"/>
+      <c r="I16" s="185" t="n"/>
+      <c r="J16" s="188" t="n"/>
+      <c r="K16" s="186" t="n"/>
+      <c r="L16" s="187" t="n">
+        <v>100</v>
+      </c>
+      <c r="M16" s="186" t="n">
+        <v>200</v>
+      </c>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="105" t="n"/>
+    </row>
+    <row r="17" ht="19.8" customHeight="1">
+      <c r="A17" s="96" t="n"/>
+      <c r="B17" s="97" t="n"/>
+      <c r="C17" s="176" t="inlineStr">
+        <is>
+          <t>CPR Card
+AED Card</t>
+        </is>
+      </c>
+      <c r="D17" s="177" t="n"/>
+      <c r="E17" s="178" t="n"/>
+      <c r="F17" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H17" s="179" t="n"/>
+      <c r="I17" s="180" t="n"/>
+      <c r="J17" s="179" t="n"/>
+      <c r="K17" s="181" t="n"/>
+      <c r="L17" s="182" t="n">
+        <v>25</v>
+      </c>
+      <c r="M17" s="181" t="n">
+        <v>125</v>
+      </c>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="105" t="n"/>
+    </row>
+    <row r="18" ht="19.8" customHeight="1">
+      <c r="A18" s="132" t="n"/>
+      <c r="B18" s="55" t="n"/>
+      <c r="C18" s="183" t="inlineStr">
+        <is>
+          <t>Wall mounted AED Cabinet
+- 1 key installed inside the break glass compartment
+- Siren with strobe (come with energizer 9v battery)
+- Door sensor</t>
+        </is>
+      </c>
+      <c r="D18" s="173" t="n"/>
+      <c r="E18" s="174" t="n"/>
+      <c r="F18" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H18" s="184" t="n"/>
+      <c r="I18" s="185" t="n"/>
+      <c r="J18" s="184" t="n"/>
+      <c r="K18" s="186" t="n"/>
+      <c r="L18" s="187" t="n">
+        <v>650</v>
+      </c>
+      <c r="M18" s="186" t="n">
+        <v>650</v>
+      </c>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="105" t="n"/>
+    </row>
+    <row r="19" ht="19.8" customHeight="1">
+      <c r="A19" s="132" t="n"/>
+      <c r="B19" s="55" t="n"/>
+      <c r="C19" s="155" t="inlineStr">
+        <is>
+          <t>AED signage
+- Size: 19(L) x 20(W) x 20(H) cm</t>
+        </is>
+      </c>
+      <c r="D19" s="173" t="n"/>
+      <c r="E19" s="173" t="n"/>
+      <c r="F19" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H19" s="184" t="n"/>
+      <c r="I19" s="185" t="n"/>
+      <c r="J19" s="188" t="n"/>
+      <c r="K19" s="186" t="n"/>
+      <c r="L19" s="187" t="n">
+        <v>75</v>
+      </c>
+      <c r="M19" s="186" t="n">
+        <v>75</v>
+      </c>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="105" t="n"/>
+    </row>
+    <row r="20" ht="19.8" customHeight="1">
+      <c r="A20" s="96" t="n"/>
+      <c r="B20" s="97" t="n"/>
+      <c r="C20" s="176" t="inlineStr">
+        <is>
+          <t>Delivery &amp; Insurance Charges</t>
+        </is>
+      </c>
+      <c r="D20" s="177" t="n"/>
+      <c r="E20" s="178" t="n"/>
+      <c r="F20" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H20" s="179" t="n"/>
+      <c r="I20" s="180" t="n"/>
+      <c r="J20" s="179" t="n"/>
+      <c r="K20" s="181" t="n"/>
+      <c r="L20" s="182" t="n">
+        <v>164</v>
+      </c>
+      <c r="M20" s="181" t="n">
+        <v>164</v>
+      </c>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="105" t="n"/>
+    </row>
+    <row r="21" ht="19.8" customHeight="1">
+      <c r="A21" s="132" t="n"/>
+      <c r="B21" s="55" t="n"/>
+      <c r="C21" s="183" t="inlineStr">
+        <is>
+          <t>Wall mounted AED Cabinet
+- 1 key installed inside the break glass compartment
+- Siren with strobe (come with energizer 9v battery)
+- Door sensor</t>
+        </is>
+      </c>
+      <c r="D21" s="173" t="n"/>
+      <c r="E21" s="174" t="n"/>
+      <c r="F21" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H21" s="184" t="n"/>
+      <c r="I21" s="185" t="n"/>
+      <c r="J21" s="184" t="n"/>
+      <c r="K21" s="186" t="n"/>
+      <c r="L21" s="187" t="n">
+        <v>650</v>
+      </c>
+      <c r="M21" s="186" t="n">
+        <v>650</v>
+      </c>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="105" t="n"/>
+    </row>
+    <row r="22" ht="19.8" customHeight="1">
+      <c r="A22" s="132" t="n"/>
+      <c r="B22" s="55" t="n"/>
+      <c r="C22" s="155" t="inlineStr">
+        <is>
+          <t>AED signage
+- Size: 19(L) x 20(W) x 20(H) cm</t>
+        </is>
+      </c>
+      <c r="D22" s="173" t="n"/>
+      <c r="E22" s="173" t="n"/>
+      <c r="F22" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H22" s="184" t="n"/>
+      <c r="I22" s="185" t="n"/>
+      <c r="J22" s="188" t="n"/>
+      <c r="K22" s="186" t="n"/>
+      <c r="L22" s="187" t="n">
+        <v>75</v>
+      </c>
+      <c r="M22" s="186" t="n">
+        <v>75</v>
+      </c>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="105" t="n"/>
+    </row>
+    <row r="23" ht="19.8" customHeight="1">
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="97" t="n"/>
+      <c r="C23" s="176" t="inlineStr">
+        <is>
+          <t>Installation of AED Cabinet (Klang Valley)
+- Mounting of the cabinet to a suitable wall location &amp; AED
+placement recommendation
+- Testing of the AED Cabinet to ensure proper functionally
+- Demonstration of how to use the AED Cabinet
+*Price varies for installation outside Klang Valley
+*Subject to terms &amp; conditions agreed between CERT Academy &amp; client</t>
+        </is>
+      </c>
+      <c r="D23" s="177" t="n"/>
+      <c r="E23" s="178" t="n"/>
+      <c r="F23" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H23" s="179" t="n"/>
+      <c r="I23" s="180" t="n"/>
+      <c r="J23" s="179" t="n"/>
+      <c r="K23" s="181" t="n"/>
+      <c r="L23" s="182" t="n">
+        <v>500</v>
+      </c>
+      <c r="M23" s="181" t="n">
+        <v>500</v>
+      </c>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="105" t="n"/>
+    </row>
+    <row r="24" ht="19.8" customHeight="1">
+      <c r="A24" s="132" t="n"/>
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="183" t="inlineStr">
+        <is>
+          <t>Electrode pad (with CPR Sensor) (5 years shelf-life)</t>
+        </is>
+      </c>
+      <c r="D24" s="173" t="n"/>
+      <c r="E24" s="174" t="n"/>
+      <c r="F24" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H24" s="184" t="n"/>
+      <c r="I24" s="185" t="n"/>
+      <c r="J24" s="184" t="n"/>
+      <c r="K24" s="186" t="n"/>
+      <c r="L24" s="187" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M24" s="186" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="105" t="n"/>
+    </row>
+    <row r="25" ht="19.8" customFormat="1" customHeight="1" s="4">
+      <c r="A25" s="132" t="n"/>
+      <c r="B25" s="55" t="n"/>
+      <c r="C25" s="155" t="inlineStr">
+        <is>
+          <t>Disposable Battery (5 Years shelf-life)</t>
+        </is>
+      </c>
+      <c r="D25" s="173" t="n"/>
+      <c r="E25" s="173" t="n"/>
+      <c r="F25" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H25" s="184" t="n"/>
+      <c r="I25" s="185" t="n"/>
+      <c r="J25" s="188" t="n"/>
+      <c r="K25" s="186" t="n"/>
+      <c r="L25" s="187" t="n">
+        <v>1420</v>
+      </c>
+      <c r="M25" s="186" t="n">
+        <v>1420</v>
+      </c>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="105" t="n"/>
+    </row>
+    <row r="26" ht="19.8" customFormat="1" customHeight="1" s="4">
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="97" t="n"/>
+      <c r="C26" s="176" t="inlineStr">
+        <is>
+          <t>CPR &amp; AED Training Course with Certificate
+(HRDCorp Claimable)
+Course Date : TBC
+Course Duration : 1 day (9.00 am - 5.00 pm)
+Course Venue : In – House (Klang Valley)</t>
+        </is>
+      </c>
+      <c r="D26" s="177" t="n"/>
+      <c r="E26" s="178" t="n"/>
+      <c r="F26" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H26" s="179" t="n"/>
+      <c r="I26" s="180" t="n"/>
+      <c r="J26" s="179" t="n"/>
+      <c r="K26" s="181" t="n"/>
+      <c r="L26" s="182" t="n">
+        <v>3900</v>
+      </c>
+      <c r="M26" s="181" t="n">
+        <v>3900</v>
+      </c>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="105" t="n"/>
+    </row>
+    <row r="27" ht="19.8" customFormat="1" customHeight="1" s="4">
+      <c r="A27" s="132" t="n"/>
+      <c r="B27" s="55" t="n"/>
+      <c r="C27" s="183" t="inlineStr">
+        <is>
+          <t>Annual AED Care Program (Valid for Klang Valley)
+An annual inspection by CERT team to ensure the AED is functioning
+properly.
+1. Physical inspection of the AEDs to check for damages or faulty.
+2. Perform diagnostic test on the AEDs.
+3. Review the AED memory to assess if there is any uncleared
+memory.
+4. Check the condition of the AED Cabinet (if applicable).
+5. Debrief to the first aid team or personnel in charge on results of
+inspection and issue/problem(s) discovered.
+6. AED briefing to the newly appointed first aider or person-in-charge
+of AED.
+7. Upgrading AHA guideline to the device when available.
+8. Download the data once AED has been activated by the company.
+***Note:
+Option 1:
+- 1 Year - Make payment on a yearly basis
+Option 2:
+- 5 years - Make payment for 5 years together to entitle
+FREE Pad + Battery worth RM 2,420.00</t>
+        </is>
+      </c>
+      <c r="D27" s="173" t="n"/>
+      <c r="E27" s="174" t="n"/>
+      <c r="F27" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="94" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H27" s="184" t="n"/>
+      <c r="I27" s="185" t="n"/>
+      <c r="J27" s="184" t="n"/>
+      <c r="K27" s="186" t="n"/>
+      <c r="L27" s="187" t="n">
+        <v>850</v>
+      </c>
+      <c r="M27" s="186" t="n">
+        <v>850</v>
+      </c>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="105" t="n"/>
+    </row>
+    <row r="28" ht="19.8" customFormat="1" customHeight="1" s="4">
+      <c r="A28" s="132" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="155" t="inlineStr">
+        <is>
+          <t>FREE AED Pad Program</t>
+        </is>
+      </c>
+      <c r="D28" s="173" t="n"/>
+      <c r="E28" s="173" t="n"/>
+      <c r="F28" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="103" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H28" s="184" t="n"/>
+      <c r="I28" s="185" t="n"/>
+      <c r="J28" s="188" t="n"/>
+      <c r="K28" s="186" t="n"/>
+      <c r="L28" s="187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="105" t="n"/>
+    </row>
+    <row r="29" ht="19.8" customFormat="1" customHeight="1" s="4">
+      <c r="A29" s="96" t="n"/>
+      <c r="B29" s="97" t="n"/>
+      <c r="C29" s="176" t="inlineStr">
+        <is>
+          <t>CERT Heartbeat Program</t>
+        </is>
+      </c>
+      <c r="D29" s="177" t="n"/>
+      <c r="E29" s="178" t="n"/>
+      <c r="F29" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="99" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H29" s="179" t="n"/>
+      <c r="I29" s="180" t="n"/>
+      <c r="J29" s="179" t="n"/>
+      <c r="K29" s="181" t="n"/>
+      <c r="L29" s="182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="105" t="n"/>
+    </row>
+    <row r="30" ht="18" customFormat="1" customHeight="1" s="5">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="56" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Total Value Excluded Tax</t>
         </is>
       </c>
-      <c r="H11" s="68" t="n"/>
-      <c r="I11" s="45" t="n"/>
-      <c r="J11" s="37" t="n"/>
-      <c r="K11" s="75" t="n"/>
-      <c r="L11" s="73" t="n"/>
-      <c r="M11" s="75" t="n"/>
-      <c r="N11" s="190" t="n"/>
-      <c r="O11" s="135" t="n"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="29" t="n"/>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="45">
+        <f>SUM(I8:I10)</f>
+        <v/>
+      </c>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="45">
+        <f>SUM(K8:K10)</f>
+        <v/>
+      </c>
+      <c r="L30" s="72" t="n"/>
+      <c r="M30" s="45">
+        <f>SUM(M8:M10)</f>
+        <v/>
+      </c>
+      <c r="N30" s="189" t="n"/>
+      <c r="O30" s="105" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="56" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sales &amp; Service Tax </t>
         </is>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G31" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="H12" s="68" t="n"/>
-      <c r="I12" s="69" t="n"/>
-      <c r="J12" s="37" t="n"/>
-      <c r="K12" s="74" t="n"/>
-      <c r="L12" s="73" t="n"/>
-      <c r="M12" s="74" t="n"/>
-      <c r="N12" s="190" t="n"/>
-      <c r="P12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="69">
+        <f>I11*0.08</f>
+        <v/>
+      </c>
+      <c r="J31" s="37" t="n"/>
+      <c r="K31" s="69">
+        <f>K11*0.08</f>
+        <v/>
+      </c>
+      <c r="L31" s="72" t="n"/>
+      <c r="M31" s="69">
+        <f>M11*0.08</f>
+        <v/>
+      </c>
+      <c r="N31" s="189" t="n"/>
+      <c r="P31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="17.4" customHeight="1">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="56" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Total Value Included Tax</t>
         </is>
       </c>
-      <c r="H13" s="68" t="n"/>
-      <c r="I13" s="45" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="75" t="n"/>
-      <c r="L13" s="73" t="n"/>
-      <c r="M13" s="75" t="n"/>
-      <c r="N13" s="190" t="n"/>
-      <c r="P13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="16.95" customHeight="1">
-      <c r="A14" s="29" t="n"/>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="45">
+        <f>I11+I12</f>
+        <v/>
+      </c>
+      <c r="J32" s="37" t="n"/>
+      <c r="K32" s="45">
+        <f>K11+K12</f>
+        <v/>
+      </c>
+      <c r="L32" s="72" t="n"/>
+      <c r="M32" s="45">
+        <f>M11+M12</f>
+        <v/>
+      </c>
+      <c r="N32" s="189" t="n"/>
+      <c r="P32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="56" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Price comparison between lowest value</t>
         </is>
       </c>
-      <c r="H14" s="70" t="n"/>
-      <c r="I14" s="45" t="n"/>
-      <c r="J14" s="37" t="n"/>
-      <c r="K14" s="61" t="n"/>
-      <c r="L14" s="72" t="n"/>
-      <c r="M14" s="88" t="n"/>
-      <c r="N14" s="190" t="n"/>
-      <c r="P14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="16.95" customHeight="1">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="H33" s="70" t="n"/>
+      <c r="I33" s="157" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="J33" s="37" t="n"/>
+      <c r="K33" s="61" t="n"/>
+      <c r="L33" s="71" t="n"/>
+      <c r="M33" s="85" t="n"/>
+      <c r="N33" s="189" t="n"/>
+      <c r="P33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="56" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>Price comparison between lowest %</t>
         </is>
       </c>
-      <c r="H15" s="70" t="n"/>
-      <c r="I15" s="71" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="67" t="n"/>
-      <c r="L15" s="72" t="n"/>
-      <c r="M15" s="89" t="n"/>
-      <c r="N15" s="190" t="n"/>
-      <c r="P15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="14.4" customHeight="1">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="56" t="inlineStr">
+      <c r="H34" s="70" t="n"/>
+      <c r="I34" s="158" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="J34" s="37" t="n"/>
+      <c r="K34" s="67" t="n"/>
+      <c r="L34" s="71" t="n"/>
+      <c r="M34" s="86" t="n"/>
+      <c r="N34" s="189" t="n"/>
+      <c r="P34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>Payment term</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F16" s="36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G16" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H16" s="191" t="inlineStr">
-        <is>
-          <t>Term : 30 days</t>
-        </is>
-      </c>
-      <c r="I16" s="192" t="n"/>
-      <c r="J16" s="115" t="inlineStr">
-        <is>
-          <t>Terms : 30 days upon invoice date</t>
-        </is>
-      </c>
-      <c r="K16" s="178" t="n"/>
-      <c r="L16" s="100" t="n"/>
-      <c r="M16" s="179" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="P16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="45.6" customHeight="1">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F35" s="36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H35" s="190" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="I35" s="191" t="n"/>
+      <c r="J35" s="147" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K35" s="177" t="n"/>
+      <c r="L35" s="97" t="inlineStr">
+        <is>
+          <t>30 Days</t>
+        </is>
+      </c>
+      <c r="M35" s="178" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="P35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="56" t="inlineStr">
         <is>
           <t>iii</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>Delivery Period</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F17" s="36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G17" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="191" t="inlineStr">
-        <is>
-          <t>Period: 4-6 weeks upon purchase order (PO) confirmation, subject to availability.</t>
-        </is>
-      </c>
-      <c r="I17" s="192" t="n"/>
-      <c r="J17" s="115" t="inlineStr">
-        <is>
-          <t>4-6 weeks if no delay</t>
-        </is>
-      </c>
-      <c r="K17" s="178" t="n"/>
-      <c r="L17" s="100" t="n"/>
-      <c r="M17" s="179" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="P17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="31.95" customHeight="1">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="D36" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F36" s="36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G36" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H36" s="190" t="inlineStr">
+        <is>
+          <t>6 - 12 weeks</t>
+        </is>
+      </c>
+      <c r="I36" s="191" t="n"/>
+      <c r="J36" s="147" t="inlineStr">
+        <is>
+          <t>4-6 weeks</t>
+        </is>
+      </c>
+      <c r="K36" s="177" t="n"/>
+      <c r="L36" s="97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="178" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="P36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n"/>
+      <c r="B37" s="56" t="inlineStr">
         <is>
           <t>iii</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>Quotation reference no.</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G18" s="34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H18" s="193" t="inlineStr">
-        <is>
-          <t>2603-11570</t>
-        </is>
-      </c>
-      <c r="I18" s="194" t="n"/>
-      <c r="J18" s="118" t="inlineStr">
-        <is>
-          <t>LeaderEnergy-DellDesktop</t>
-        </is>
-      </c>
-      <c r="K18" s="195" t="n"/>
-      <c r="L18" s="196" t="n"/>
-      <c r="M18" s="179" t="n"/>
-      <c r="N18" s="18" t="n"/>
-      <c r="P18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="127" t="n"/>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="D37" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F37" s="36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G37" s="34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H37" s="192" t="inlineStr">
+        <is>
+          <t>260206/RM/LSE/1/HK</t>
+        </is>
+      </c>
+      <c r="I37" s="193" t="n"/>
+      <c r="J37" s="150" t="inlineStr">
+        <is>
+          <t>LEA/0004/2026</t>
+        </is>
+      </c>
+      <c r="K37" s="194" t="n"/>
+      <c r="L37" s="195" t="inlineStr">
+        <is>
+          <t>Q/069(RV2)/26-SHD</t>
+        </is>
+      </c>
+      <c r="M37" s="178" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="P37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="132" t="n"/>
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C19" s="125" t="inlineStr">
+      <c r="C38" s="130" t="inlineStr">
         <is>
           <t>Procurement Recommendation</t>
         </is>
       </c>
-      <c r="D19" s="162" t="n"/>
-      <c r="E19" s="162" t="n"/>
-      <c r="F19" s="162" t="n"/>
-      <c r="G19" s="162" t="n"/>
-      <c r="H19" s="46" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I19" s="47" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J19" s="49" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K19" s="48" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L19" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M19" s="65" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N19" s="18" t="n"/>
-      <c r="P19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="409.05" customHeight="1">
-      <c r="B20" s="57" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C20" s="197" t="n"/>
-      <c r="D20" s="174" t="n"/>
-      <c r="E20" s="174" t="n"/>
-      <c r="F20" s="174" t="n"/>
-      <c r="G20" s="174" t="n"/>
-      <c r="H20" s="174" t="n"/>
-      <c r="I20" s="174" t="n"/>
-      <c r="J20" s="174" t="n"/>
-      <c r="K20" s="174" t="n"/>
-      <c r="L20" s="174" t="n"/>
-      <c r="M20" s="175" t="n"/>
-      <c r="N20" s="18" t="n"/>
-    </row>
-    <row r="21" ht="14.4" customHeight="1">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="D38" s="161" t="n"/>
+      <c r="E38" s="161" t="n"/>
+      <c r="F38" s="161" t="n"/>
+      <c r="G38" s="161" t="n"/>
+      <c r="H38" s="46" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I38" s="47" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J38" s="49" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K38" s="48" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L38" s="38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M38" s="65" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N38" s="18" t="n"/>
+      <c r="P38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="57" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C39" s="196" t="n"/>
+      <c r="D39" s="173" t="n"/>
+      <c r="E39" s="173" t="n"/>
+      <c r="F39" s="173" t="n"/>
+      <c r="G39" s="173" t="n"/>
+      <c r="H39" s="173" t="n"/>
+      <c r="I39" s="173" t="n"/>
+      <c r="J39" s="173" t="n"/>
+      <c r="K39" s="173" t="n"/>
+      <c r="L39" s="173" t="n"/>
+      <c r="M39" s="174" t="n"/>
+      <c r="N39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="58" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C40" s="54" t="inlineStr">
         <is>
           <t>End User Assessment and Recommendation</t>
         </is>
       </c>
-      <c r="D21" s="39" t="n"/>
-      <c r="E21" s="39" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K21" s="40" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L21" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M21" s="42" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="38.25" customHeight="1">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C22" s="132" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D22" s="174" t="n"/>
-      <c r="E22" s="174" t="n"/>
-      <c r="F22" s="174" t="n"/>
-      <c r="G22" s="174" t="n"/>
-      <c r="H22" s="174" t="n"/>
-      <c r="I22" s="174" t="n"/>
-      <c r="J22" s="174" t="n"/>
-      <c r="K22" s="174" t="n"/>
-      <c r="L22" s="174" t="n"/>
-      <c r="M22" s="198" t="n"/>
-      <c r="N22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="14.4" customHeight="1">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="57" t="inlineStr">
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K40" s="40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L40" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M40" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N40" s="18" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C41" s="137" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D41" s="173" t="n"/>
+      <c r="E41" s="173" t="n"/>
+      <c r="F41" s="173" t="n"/>
+      <c r="G41" s="173" t="n"/>
+      <c r="H41" s="173" t="n"/>
+      <c r="I41" s="173" t="n"/>
+      <c r="J41" s="173" t="n"/>
+      <c r="K41" s="173" t="n"/>
+      <c r="L41" s="173" t="n"/>
+      <c r="M41" s="197" t="n"/>
+      <c r="N41" s="18" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="57" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C23" s="41" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E23" s="38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="L23" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="M23" s="42" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="24.75" customHeight="1">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="60" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C24" s="134" t="n"/>
-      <c r="D24" s="174" t="n"/>
-      <c r="E24" s="174" t="n"/>
-      <c r="F24" s="174" t="n"/>
-      <c r="G24" s="174" t="n"/>
-      <c r="H24" s="174" t="n"/>
-      <c r="I24" s="174" t="n"/>
-      <c r="J24" s="174" t="n"/>
-      <c r="K24" s="174" t="n"/>
-      <c r="L24" s="174" t="n"/>
-      <c r="M24" s="198" t="n"/>
-      <c r="N24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="25.95" customFormat="1" customHeight="1" s="4">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E42" s="38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L42" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M42" s="42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N42" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C43" s="139" t="n"/>
+      <c r="D43" s="173" t="n"/>
+      <c r="E43" s="173" t="n"/>
+      <c r="F43" s="173" t="n"/>
+      <c r="G43" s="173" t="n"/>
+      <c r="H43" s="173" t="n"/>
+      <c r="I43" s="173" t="n"/>
+      <c r="J43" s="173" t="n"/>
+      <c r="K43" s="173" t="n"/>
+      <c r="L43" s="173" t="n"/>
+      <c r="M43" s="197" t="n"/>
+      <c r="N43" s="18" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Verified by:</t>
         </is>
       </c>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Checked by:</t>
         </is>
       </c>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>Recommended by:</t>
         </is>
       </c>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>Approved by:</t>
         </is>
       </c>
-      <c r="N25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="17.4" customFormat="1" customHeight="1" s="4">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="199" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="10" t="n"/>
-      <c r="N26" s="18" t="n"/>
-    </row>
-    <row r="27" ht="17.4" customFormat="1" customHeight="1" s="4">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="199" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="18" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customFormat="1" customHeight="1" s="4">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="N44" s="18" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="198" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="18" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="198" t="n"/>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="13" t="n"/>
+      <c r="I46" s="13" t="n"/>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="18" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Lee</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="199" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="10" t="n"/>
-      <c r="N28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="15.6" customFormat="1" customHeight="1" s="4">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="81" t="inlineStr">
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="198" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="16" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="16" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="18" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="78" t="inlineStr">
         <is>
           <t>Lee Pei Ru</t>
         </is>
       </c>
-      <c r="D29" s="77" t="n"/>
-      <c r="E29" s="78" t="inlineStr">
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="75" t="inlineStr">
         <is>
           <t>Yohana Yusrin</t>
         </is>
       </c>
-      <c r="F29" s="200" t="n"/>
-      <c r="G29" s="77" t="n"/>
-      <c r="H29" s="200" t="inlineStr">
+      <c r="F48" s="199" t="n"/>
+      <c r="G48" s="74" t="n"/>
+      <c r="H48" s="199" t="inlineStr">
         <is>
           <t>Ernest Lim</t>
         </is>
       </c>
-      <c r="I29" s="77" t="n"/>
-      <c r="J29" s="200" t="inlineStr">
+      <c r="I48" s="74" t="n"/>
+      <c r="J48" s="199" t="inlineStr">
         <is>
           <t>Sivakumar</t>
         </is>
       </c>
-      <c r="K29" s="200" t="n"/>
-      <c r="L29" s="200" t="inlineStr">
+      <c r="K48" s="199" t="n"/>
+      <c r="L48" s="199" t="inlineStr">
         <is>
           <t>Chung Shi Huan</t>
         </is>
       </c>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="18" customFormat="1" customHeight="1" s="5">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="77" t="inlineStr">
+      <c r="M48" s="79" t="n"/>
+      <c r="N48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="74" t="inlineStr">
         <is>
           <t>Asst Procurement Manager</t>
         </is>
       </c>
-      <c r="D30" s="77" t="n"/>
-      <c r="E30" s="77" t="inlineStr">
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="74" t="inlineStr">
         <is>
           <t>Senior Project Engineering</t>
         </is>
       </c>
-      <c r="F30" s="77" t="n"/>
-      <c r="G30" s="77" t="n"/>
-      <c r="H30" s="200" t="inlineStr">
+      <c r="F49" s="74" t="n"/>
+      <c r="G49" s="74" t="n"/>
+      <c r="H49" s="199" t="inlineStr">
         <is>
           <t>Snr. Procurement Manager</t>
         </is>
       </c>
-      <c r="I30" s="200" t="n"/>
-      <c r="J30" s="77" t="inlineStr">
+      <c r="I49" s="199" t="n"/>
+      <c r="J49" s="74" t="inlineStr">
         <is>
           <t>Head of IT</t>
         </is>
       </c>
-      <c r="K30" s="77" t="n"/>
-      <c r="L30" s="77" t="inlineStr">
+      <c r="K49" s="74" t="n"/>
+      <c r="L49" s="74" t="inlineStr">
         <is>
           <t>Head of Engineering</t>
         </is>
       </c>
-      <c r="M30" s="82" t="n"/>
-      <c r="N30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="83" t="n"/>
-      <c r="D31" s="79" t="n"/>
-      <c r="E31" s="77" t="n"/>
-      <c r="F31" s="77" t="n"/>
-      <c r="G31" s="77" t="n"/>
-      <c r="H31" s="77" t="n"/>
-      <c r="I31" s="77" t="n"/>
-      <c r="J31" s="201" t="n"/>
-      <c r="K31" s="79" t="n"/>
-      <c r="L31" s="201" t="n"/>
-      <c r="M31" s="84" t="n"/>
-      <c r="N31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="17.4" customHeight="1">
-      <c r="A32" s="18" t="n"/>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="202" t="n"/>
-      <c r="M32" s="23" t="n"/>
-      <c r="N32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="N33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="C34" s="28" t="n"/>
-    </row>
-    <row r="35">
-      <c r="C35" s="28" t="n"/>
-      <c r="L35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="C36" s="28" t="n"/>
-      <c r="L36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="28" t="n"/>
-      <c r="L37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="C38" s="28" t="n"/>
-    </row>
-    <row r="39">
-      <c r="C39" s="28" t="n"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="28" t="n"/>
-    </row>
-    <row r="41">
-      <c r="C41" s="28" t="n"/>
+      <c r="M49" s="79" t="n"/>
+      <c r="N49" s="18" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n"/>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="80" t="n"/>
+      <c r="D50" s="76" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="74" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="74" t="n"/>
+      <c r="J50" s="200" t="n"/>
+      <c r="K50" s="76" t="n"/>
+      <c r="L50" s="200" t="n"/>
+      <c r="M50" s="81" t="n"/>
+      <c r="N50" s="18" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="24" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="13" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="201" t="n"/>
+      <c r="M51" s="23" t="n"/>
+      <c r="N51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="N52" s="18" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="28" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="28" t="n"/>
+      <c r="L54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="28" t="n"/>
+      <c r="L55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="28" t="n"/>
+      <c r="L56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="28" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="28" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="28" t="n"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="28" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="61">
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="L17:M17"/>
+    <mergeCell ref="O29:W29"/>
+    <mergeCell ref="O20:W20"/>
     <mergeCell ref="L16:M16"/>
+    <mergeCell ref="O26:W26"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C24:M24"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="B1:M1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="O22:W22"/>
     <mergeCell ref="B5:E7"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="O16:W16"/>
+    <mergeCell ref="O25:W25"/>
+    <mergeCell ref="O21:W21"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C20:M20"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="L18:M18"/>
+    <mergeCell ref="O27:W27"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="O12:W12"/>
     <mergeCell ref="O8:W8"/>
     <mergeCell ref="C22:M22"/>
+    <mergeCell ref="O17:W17"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="O11:W11"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C13:E13"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H5:M5"/>
     <mergeCell ref="J16:K16"/>
+    <mergeCell ref="O14:W14"/>
+    <mergeCell ref="O23:W23"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="O13:W13"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="C15:E15"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="O19:W19"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="O28:W28"/>
     <mergeCell ref="L6:M6"/>
+    <mergeCell ref="O24:W24"/>
+    <mergeCell ref="O15:W15"/>
+    <mergeCell ref="O18:W18"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C25:E25"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="E11:F13 E14:E15">
